--- a/order_generation/PO_excel_export/test-4.xlsx
+++ b/order_generation/PO_excel_export/test-4.xlsx
@@ -339,36 +339,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1457325" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -796,7 +766,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年12月30日</t>
+          <t>2026年02月02日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -868,36 +838,63 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>EEHB-NBB-3</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n"/>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>猪鬃红色胶皮天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+          <t>圆形品牌logo贴纸</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>3.03</v>
+        <v>0.05</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>散货</t>
+        </is>
+      </c>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>ST1122-4</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>猪鬃木纹天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -948,7 +945,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
+          <t>吉秀地址：宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -964,11 +961,7 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>款到发货</t>
-        </is>
-      </c>
+      <c r="B13" s="25" t="inlineStr"/>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
@@ -1059,11 +1052,7 @@
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>备注:打样2套,含税运</t>
-        </is>
-      </c>
+      <c r="A19" s="25" t="inlineStr"/>
       <c r="B19" s="25" t="n"/>
       <c r="C19" s="25" t="n"/>
       <c r="D19" s="25" t="n"/>
@@ -1387,6 +1376,5 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.78740157480315" bottom="0.590551181102362" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="360" verticalDpi="360"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>